--- a/Framework_Inputs/WLS/Work Load Model Template_v1.0.xlsx
+++ b/Framework_Inputs/WLS/Work Load Model Template_v1.0.xlsx
@@ -1,33 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Performance\Non-Project\Specialization\Assets &amp; Accelarators\Execution Scenario Automator\FrameworkRepo\Framework_Inputs\WLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\WLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE658535-603E-437F-8CA2-8A9C00D621A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8100" windowHeight="4660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IB" sheetId="7" r:id="rId1"/>
     <sheet name="MB" sheetId="8" r:id="rId2"/>
     <sheet name="CBS" sheetId="9" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
   <si>
     <t>Transactions</t>
   </si>
@@ -120,13 +132,31 @@
   </si>
   <si>
     <t>Delete_User</t>
+  </si>
+  <si>
+    <t>IB_Add</t>
+  </si>
+  <si>
+    <t>IB_Change</t>
+  </si>
+  <si>
+    <t>IB_Remove</t>
+  </si>
+  <si>
+    <t>IB_Create</t>
+  </si>
+  <si>
+    <t>IB_Update</t>
+  </si>
+  <si>
+    <t>IB_Delete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,6 +173,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Trebuchet MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -202,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -211,6 +247,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -492,37 +531,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:W7"/>
-  <sheetFormatPr defaultColWidth="19.26953125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="19.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="25">
+    <row r="1" spans="1:23" ht="25.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,7 +836,7 @@
         <v>72</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="2"/>
+        <f>K4*60%</f>
         <v>102</v>
       </c>
       <c r="I4" s="3">
@@ -819,7 +858,7 @@
         <v>240</v>
       </c>
       <c r="N4" s="3">
-        <f t="shared" si="5"/>
+        <f>K4*2</f>
         <v>340</v>
       </c>
       <c r="O4" s="3">
@@ -850,7 +889,7 @@
         <v>168</v>
       </c>
       <c r="V4" s="3">
-        <f t="shared" si="11"/>
+        <f>K4/L4</f>
         <v>8.5</v>
       </c>
       <c r="W4" s="3">
@@ -863,91 +902,86 @@
       </c>
       <c r="B5" s="3">
         <f t="shared" ref="B5:B7" si="14">K5*10%</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3">
         <f>L5*10%</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D7" si="15">C5*$B$2</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" ref="E5:E7" si="16">N5*10%</f>
-        <v>0</v>
+        <f>K5*30%</f>
+        <v>36</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F7" si="17">O5*10%</f>
-        <v>0</v>
+        <f>L5*30%</f>
+        <v>9</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" ref="G5:G7" si="18">P5*10%</f>
-        <v>0</v>
+        <f>M5*30%</f>
+        <v>75</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" ref="H5:H7" si="19">Q5*10%</f>
-        <v>0</v>
+        <f>K5*60%</f>
+        <v>72</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" ref="I5:I7" si="20">R5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="I5" si="16">L5*60%</f>
+        <v>18</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" ref="J5:J7" si="21">S5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="J5" si="17">I5*$B$2</f>
+        <v>216</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" ref="K5:K7" si="22">T5*10%</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L5" s="3">
-        <f t="shared" ref="L5:L7" si="23">U5*10%</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M5" s="3">
-        <f t="shared" ref="M5:M7" si="24">V5*10%</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="N5" s="3">
-        <f t="shared" ref="N5:N7" si="25">W5*10%</f>
-        <v>0</v>
+        <f>K5*2</f>
+        <v>240</v>
       </c>
       <c r="O5" s="3">
-        <f t="shared" ref="O5:O7" si="26">X5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="O5" si="18">L5</f>
+        <v>30</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" ref="P5:P7" si="27">Y5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="P5" si="19">O5*$B$2</f>
+        <v>360</v>
       </c>
       <c r="Q5" s="3">
-        <f t="shared" ref="Q5:Q7" si="28">Z5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="Q5" si="20">N5/O5</f>
+        <v>8</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" ref="R5:R7" si="29">AA5*10%</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" ref="S5:S7" si="30">AB5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="S5" si="21">K5*70%</f>
+        <v>84</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" ref="T5:T7" si="31">AC5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="T5" si="22">L5*70%</f>
+        <v>21</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" ref="U5:U7" si="32">AD5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="U5" si="23">T5*$B$2</f>
+        <v>252</v>
       </c>
       <c r="V5" s="3">
-        <f t="shared" ref="V5:V7" si="33">AE5*10%</f>
-        <v>0</v>
+        <f>K5/L5</f>
+        <v>4</v>
       </c>
       <c r="W5" s="3">
-        <f t="shared" ref="W5:W7" si="34">AF5*10%</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -955,92 +989,87 @@
         <v>29</v>
       </c>
       <c r="B6" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" ref="B6" si="24">K6*10%</f>
+        <v>36</v>
       </c>
       <c r="C6" s="3">
-        <f t="shared" ref="C6:C7" si="35">L6*10%</f>
-        <v>0</v>
+        <f>L6*10%</f>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="D6" si="25">C6*$B$2</f>
+        <v>48</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>K6*30%</f>
+        <v>108</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>L6*30%</f>
+        <v>12</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>M6*30%</f>
+        <v>90</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>K6*60%</f>
+        <v>216</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" ref="I6" si="26">L6*60%</f>
+        <v>24</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" ref="J6" si="27">I6*$B$2</f>
+        <v>288</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>K6*2</f>
+        <v>720</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" ref="O6" si="28">L6</f>
+        <v>40</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" ref="P6" si="29">O6*$B$2</f>
+        <v>480</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" ref="Q6" si="30">N6/O6</f>
+        <v>18</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" ref="S6" si="31">K6*70%</f>
+        <v>251.99999999999997</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" ref="T6" si="32">L6*70%</f>
+        <v>28</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f t="shared" ref="U6" si="33">T6*$B$2</f>
+        <v>336</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f>K6/L6</f>
+        <v>9</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1048,92 +1077,87 @@
         <v>30</v>
       </c>
       <c r="B7" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" ref="B7" si="34">K7*10%</f>
+        <v>32</v>
       </c>
       <c r="C7" s="3">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f>L7*10%</f>
+        <v>1</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="D7" si="35">C7*$B$2</f>
+        <v>12</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>K7*30%</f>
+        <v>96</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>L7*30%</f>
+        <v>3</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>M7*30%</f>
+        <v>36</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="19"/>
-        <v>0</v>
+        <f>K7*60%</f>
+        <v>192</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" ref="I7" si="36">L7*60%</f>
+        <v>6</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" ref="J7" si="37">I7*$B$2</f>
+        <v>72</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="L7" s="3">
-        <f t="shared" si="23"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M7" s="3">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7" s="3">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f>K7*2</f>
+        <v>640</v>
       </c>
       <c r="O7" s="3">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" ref="O7" si="38">L7</f>
+        <v>10</v>
       </c>
       <c r="P7" s="3">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" ref="P7" si="39">O7*$B$2</f>
+        <v>120</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" ref="Q7" si="40">N7/O7</f>
+        <v>64</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" ref="S7" si="41">K7*70%</f>
+        <v>224</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" ref="T7" si="42">L7*70%</f>
+        <v>7</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f t="shared" ref="U7" si="43">T7*$B$2</f>
+        <v>84</v>
       </c>
       <c r="V7" s="3">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f>K7/L7</f>
+        <v>32</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1142,36 +1166,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.453125" customWidth="1"/>
-    <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="25">
+    <row r="1" spans="1:23" ht="25.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1512,37 +1536,37 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:W7"/>
-  <sheetFormatPr defaultColWidth="19.26953125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="19.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="25">
+    <row r="1" spans="1:23" ht="25.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1614,8 +1638,8 @@
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="3" t="s">
-        <v>22</v>
+      <c r="A2" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="B2" s="3">
         <v>12</v>
@@ -1702,8 +1726,8 @@
       </c>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="3" t="s">
-        <v>23</v>
+      <c r="A3" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -1790,8 +1814,8 @@
       </c>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="3" t="s">
-        <v>24</v>
+      <c r="A4" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -1878,282 +1902,267 @@
       </c>
     </row>
     <row r="5" spans="1:23">
-      <c r="A5" s="3" t="s">
-        <v>28</v>
+      <c r="A5" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B5" s="3">
-        <f t="shared" ref="B5:C7" si="14">K5*10%</f>
-        <v>0</v>
+        <f>K5*10%</f>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
         <f>L5*10%</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>M5*10%</f>
+        <v>12</v>
       </c>
       <c r="E5" s="3">
-        <f t="shared" ref="E5:T7" si="15">N5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="E5" si="14">K5*30%</f>
+        <v>54</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="F5" si="15">L5*30%</f>
+        <v>12</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="G5" si="16">F5*$B$2</f>
+        <v>144</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="H5" si="17">K5*60%</f>
+        <v>108</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="I5" si="18">L5*60%</f>
+        <v>24</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="J5" si="19">I5*$B$2</f>
+        <v>288</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="N5" si="20">K5*2</f>
+        <v>360</v>
       </c>
       <c r="O5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="O5" si="21">L5</f>
+        <v>40</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="P5" si="22">O5*$B$2</f>
+        <v>480</v>
       </c>
       <c r="Q5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="Q5" si="23">N5/O5</f>
+        <v>9</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="S5" si="24">K5*70%</f>
+        <v>125.99999999999999</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="T5" si="25">L5*70%</f>
+        <v>28</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" ref="U5:W7" si="16">AD5*10%</f>
-        <v>0</v>
+        <f t="shared" ref="U5" si="26">T5*$B$2</f>
+        <v>336</v>
       </c>
       <c r="V5" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" ref="V5" si="27">K5/L5</f>
+        <v>4.5</v>
       </c>
       <c r="W5" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
+      <c r="A6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B6" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>K6*10%</f>
+        <v>30</v>
       </c>
       <c r="C6" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>L6*10%</f>
+        <v>2</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>M6*10%</f>
+        <v>18</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="E6" si="28">K6*30%</f>
+        <v>90</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="F6" si="29">L6*30%</f>
+        <v>6</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="G6" si="30">F6*$B$2</f>
+        <v>72</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="H6" si="31">K6*60%</f>
+        <v>180</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="I6" si="32">L6*60%</f>
+        <v>12</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="J6" si="33">I6*$B$2</f>
+        <v>144</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="N6" si="34">K6*2</f>
+        <v>600</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="O6" si="35">L6</f>
+        <v>20</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="P6" si="36">O6*$B$2</f>
+        <v>240</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="Q6" si="37">N6/O6</f>
+        <v>30</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="S6" si="38">K6*70%</f>
+        <v>210</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="T6" si="39">L6*70%</f>
+        <v>14</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" ref="U6" si="40">T6*$B$2</f>
+        <v>168</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" ref="V6" si="41">K6/L6</f>
+        <v>15</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3">
+        <f>K7*10%</f>
+        <v>35</v>
+      </c>
+      <c r="C7" s="3">
+        <f>L7*10%</f>
+        <v>3</v>
+      </c>
+      <c r="D7" s="3">
+        <f>M7*10%</f>
+        <v>10</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" ref="E7" si="42">K7*30%</f>
+        <v>105</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" ref="F7" si="43">L7*30%</f>
+        <v>9</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" ref="G7" si="44">F7*$B$2</f>
+        <v>108</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" ref="H7" si="45">K7*60%</f>
+        <v>210</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" ref="I7" si="46">L7*60%</f>
+        <v>18</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" ref="J7" si="47">I7*$B$2</f>
+        <v>216</v>
+      </c>
+      <c r="K7" s="3">
+        <v>350</v>
+      </c>
+      <c r="L7" s="3">
         <v>30</v>
       </c>
-      <c r="B7" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
       <c r="M7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="N7" si="48">K7*2</f>
+        <v>700</v>
       </c>
       <c r="O7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="O7" si="49">L7</f>
+        <v>30</v>
       </c>
       <c r="P7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="P7" si="50">O7*$B$2</f>
+        <v>360</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="Q7" si="51">N7/O7</f>
+        <v>23.333333333333332</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="S7" si="52">K7*70%</f>
+        <v>244.99999999999997</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" ref="T7" si="53">L7*70%</f>
+        <v>21</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" ref="U7" si="54">T7*$B$2</f>
+        <v>252</v>
       </c>
       <c r="V7" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" ref="V7" si="55">K7/L7</f>
+        <v>11.666666666666666</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2394,13 +2403,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E9485FD-6F58-4F56-ABB4-E3FAF1846CCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E9485FD-6F58-4F56-ABB4-E3FAF1846CCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3bffceee-05df-448a-9da5-35921f8de3e1"/>
+    <ds:schemaRef ds:uri="edf95c69-45f6-4b27-bec3-1dc5ad170efe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DAD3A61-EAD6-49BE-8134-F637A6B20C0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DAD3A61-EAD6-49BE-8134-F637A6B20C0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351725F1-7796-4DAF-943B-A46C7DCADE0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351725F1-7796-4DAF-943B-A46C7DCADE0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Framework_Inputs/WLS/Work Load Model Template_v1.0.xlsx
+++ b/Framework_Inputs/WLS/Work Load Model Template_v1.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Pictures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\WLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7196CDE1-224B-4BB4-B0E1-1A2CC4F84F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C635BA-BC86-48DE-9379-FC48BB6774E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,10 +108,10 @@
     <t>Home_Page</t>
   </si>
   <si>
-    <t>Search _For_Vets</t>
-  </si>
-  <si>
     <t>Owners</t>
+  </si>
+  <si>
+    <t>Search_For_Vets</t>
   </si>
 </sst>
 </file>
@@ -675,7 +675,7 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -855,18 +855,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1087,18 +1087,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351725F1-7796-4DAF-943B-A46C7DCADE0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DAD3A61-EAD6-49BE-8134-F637A6B20C0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DAD3A61-EAD6-49BE-8134-F637A6B20C0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351725F1-7796-4DAF-943B-A46C7DCADE0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
